--- a/resources/plantillas/registro-asistencia.xlsx
+++ b/resources/plantillas/registro-asistencia.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="20">
   <si>
     <t>UNIVERSIDAD NACIONAL SANTIAGO ANTÚNEZ DE MAYOLO</t>
   </si>
@@ -1482,18 +1482,10 @@
       <c r="Z8" s="29"/>
       <c r="AA8" s="29"/>
       <c r="AB8" s="56"/>
-      <c r="AC8" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD8" s="30" t="s">
-        <v>11</v>
-      </c>
-      <c r="AE8" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="AF8" s="71" t="s">
-        <v>13</v>
-      </c>
+      <c r="AC8" s="62"/>
+      <c r="AD8" s="30"/>
+      <c r="AE8" s="30"/>
+      <c r="AF8" s="71"/>
       <c r="AG8" s="65" t="s">
         <v>8</v>
       </c>
@@ -2934,9 +2926,7 @@
       </c>
     </row>
     <row r="46" spans="1:33" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="74" t="s">
-        <v>19</v>
-      </c>
+      <c r="A46" s="74"/>
       <c r="B46" s="74"/>
       <c r="C46" s="74"/>
       <c r="D46" s="74"/>
